--- a/20130199_TestDesign.xlsx
+++ b/20130199_TestDesign.xlsx
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="25.5" spans="1:6">
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" ht="38.25" spans="1:6">
+    <row r="18" ht="25.5" spans="1:6">
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F59" s="5"/>
     </row>
-    <row r="60" ht="38.25" spans="1:6">
+    <row r="60" ht="25.5" spans="1:6">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>

--- a/20130199_TestDesign.xlsx
+++ b/20130199_TestDesign.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,22 +112,22 @@
     <t>Kiểm tra nhập vào phạm vi giá tùy chỉnh.</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép nhập chữ vào ô nhập bên trái trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép nhập chữ vào ô nhập bên trái trong khoảng giá .</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép nhập chữ vào ô nhập bên phải trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép nhập chữ vào ô nhập bên phải trong khoảng giá .</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép nhập ký tự đặc biệt vào ô nhập bên trái trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép nhập ký tự đặc biệt vào ô nhập bên trái trong khoảng giá .</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép nhập ký tự đặc biệt vào ô nhập bên phải trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép nhập ký tự đặc biệt vào ô nhập bên phải trong khoảng giá .</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép giá trị nhập vào của ô bên trái lớn hơn ô bên phải trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép giá trị nhập vào của ô bên trái lớn hơn ô bên phải trong khoảng giá .</t>
   </si>
   <si>
-    <t>Kiểm tra không cho phép nhập giá trị của ô bên trái bằng với giá trị của ô bên phải trong khoảng giá thành công.</t>
+    <t>Kiểm tra không cho phép nhập giá trị của ô bên trái bằng với giá trị của ô bên phải trong khoảng giá .</t>
   </si>
   <si>
     <t>Kiểm tra xóa phạm vi giá đã chọn bằng cách bấm nút [Xóa]</t>
@@ -145,118 +145,118 @@
     <t>Success</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có dịch vụ [Trả góp 0%] thành công.</t>
+    <t>Lọc các sản phẩm có dịch vụ [Trả góp 0%] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2h] thành công.</t>
+    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2h] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2h] và [Trả góp 0%] thành công.</t>
+    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2h] và [Trả góp 0%] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm được khuyến mãi [TOP DEAL Siêu rẻ] thành công.</t>
+    <t>Lọc sản phẩm được khuyến mãi [TOP DEAL Siêu rẻ] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có khuyến mãi [FREESHIP XTRA] thành công.</t>
+    <t>Lọc sản phẩm có khuyến mãi [FREESHIP XTRA] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có khuyến mãi [FREESHIP XTRA] và [TOP DEAL Siêu rẻ] thành công.</t>
+    <t>Lọc sản phẩm có khuyến mãi [FREESHIP XTRA] và [TOP DEAL Siêu rẻ] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có đánh giá [từ 3 sao] thành công.</t>
+    <t>Lọc sản phẩm có đánh giá [từ 3 sao] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có đánh giá [từ 4 sao] thành công.</t>
+    <t>Lọc sản phẩm có đánh giá [từ 4 sao] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có đánh giá [từ 5 sao] thành công.</t>
+    <t>Lọc sản phẩm có đánh giá [từ 5 sao] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có giá dưới 2.000.000 thành công.</t>
+    <t>Lọc sản phẩm có giá dưới 2.000.000 .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có giá từ 2.000.000 đến 4.000.000 thành công.</t>
+    <t>Lọc sản phẩm có giá từ 2.000.000 đến 4.000.000 .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có giá từ 4.000.000 đến 12.000.000 thành công.</t>
+    <t>Lọc sản phẩm có giá từ 4.000.000 đến 12.000.000 .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có giá trên 12.000.000 thành công.</t>
+    <t>Lọc các sản phẩm có giá trên 12.000.000 .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có giá dưới 2.000 thành công.</t>
+    <t>Lọc sản phẩm có giá dưới 2.000 .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có giá trên 1.200.000.000 thành công.</t>
+    <t>Lọc sản phẩm có giá trên 1.200.000.000 .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có giá từ 1.200.000 đến 1.200.000 thành công.</t>
+    <t>Lọc các sản phẩm có giá từ 1.200.000 đến 1.200.000 .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có giá từ 1.200.000 đến 2.200.000 thành công.</t>
+    <t>Lọc các sản phẩm có giá từ 1.200.000 đến 2.200.000 .</t>
   </si>
   <si>
     <t>Lọc các sản phẩm có giá từ 3.200.000 đến 1.200.000 thất bại.</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có ROM [128GB] thành công.</t>
+    <t>Lọc các sản phẩm có ROM [128GB] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có ROM [8GB] thành công.</t>
+    <t>Lọc sản phẩm có ROM [8GB] .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có ROM [128GB] hoặc [256GB] thành công.</t>
+    <t>Lọc sản phẩm có ROM [128GB] hoặc [256GB] .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có thương hiệu "Samsung" thành công.</t>
+    <t>Lọc các sản phẩm có thương hiệu "Samsung" .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có thương hiệu "Samsung" hoặc "Xiaomi" thành công.</t>
+    <t>Lọc các sản phẩm có thương hiệu "Samsung" hoặc "Xiaomi" .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera sau trên 16MP thành công.</t>
+    <t>Lọc sản phẩm có camera sau trên 16MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera sau dưới 8MP thành công.</t>
+    <t>Lọc sản phẩm có camera sau dưới 8MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera sau từ 8MP đến 10MP thành công.</t>
+    <t>Lọc sản phẩm có camera sau từ 8MP đến 10MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera sau từ 8MP đến 10MP hoặc tên 16MP thành công.</t>
+    <t>Lọc sản phẩm có camera sau từ 8MP đến 10MP hoặc tên 16MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera trước lớn hơn 12MP thành công.</t>
+    <t>Lọc sản phẩm có camera trước lớn hơn 12MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera trước dưới 8MP thành công.</t>
+    <t>Lọc sản phẩm có camera trước dưới 8MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera trước từ 5MP đến 8MP thành công.</t>
+    <t>Lọc sản phẩm có camera trước từ 5MP đến 8MP .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có camera trước từ 5MP đến 8MP hoặc trên 12MP thành công.</t>
+    <t>Lọc sản phẩm có camera trước từ 5MP đến 8MP hoặc trên 12MP .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có màu đen thành công.</t>
+    <t>Lọc các sản phẩm có màu đen .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có màu đen hoặc xanh lá xây thành công.</t>
+    <t>Lọc các sản phẩm có màu đen hoặc xanh lá xây .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm được cung cấp bởi Tiki Trading thành công.</t>
+    <t>Lọc các sản phẩm được cung cấp bởi Tiki Trading .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm được cung cấp bới "Tiki Trading" hoặc "Thế Giới Di Động Official" thành công.</t>
+    <t>Lọc các sản phẩm được cung cấp bới "Tiki Trading" hoặc "Thế Giới Di Động Official" .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có camera sau trên 16MP và có màu xanh dương thành công.</t>
+    <t>Lọc các sản phẩm có camera sau trên 16MP và có màu xanh dương .</t>
   </si>
   <si>
-    <t>Lọc các sản phẩm có thương hiệu "Samsung" hoặc "Xiaomi" và có ROM là 128GB thành công.</t>
+    <t>Lọc các sản phẩm có thương hiệu "Samsung" hoặc "Xiaomi" và có ROM là 128GB .</t>
   </si>
   <si>
-    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2H] và dịch vụ [Trả góp 0%], có thương thiệu là SamSung hoặc Oppo, có màu đen, vàng hoặc xanh dương thành công.</t>
+    <t>Lọc sản phẩm có dịch vụ [NOW Giao siêu tốc 2H] và dịch vụ [Trả góp 0%], có thương thiệu là SamSung hoặc Oppo, có màu đen, vàng hoặc xanh dương .</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" ht="38.25" spans="1:6">
+    <row r="19" ht="25.5" spans="1:6">
       <c r="A19" s="7"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" ht="38.25" spans="1:6">
+    <row r="20" ht="25.5" spans="1:6">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" ht="25.5" spans="1:6">
+    <row r="24" spans="1:6">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
         <v>36</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" ht="25.5" spans="1:6">
+    <row r="30" spans="1:6">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" ht="25.5" spans="1:6">
+    <row r="31" spans="1:6">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" ht="25.5" spans="1:6">
+    <row r="32" spans="1:6">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F32" s="5"/>
     </row>
-    <row r="33" ht="25.5" spans="1:6">
+    <row r="33" spans="1:6">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F35" s="5"/>
     </row>
-    <row r="36" ht="25.5" spans="1:6">
+    <row r="36" spans="1:6">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" ht="25.5" spans="1:6">
+    <row r="38" spans="1:6">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F41" s="5"/>
     </row>
-    <row r="42" ht="25.5" spans="1:6">
+    <row r="42" spans="1:6">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" ht="25.5" spans="1:6">
+    <row r="44" spans="1:6">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F44" s="5"/>
     </row>
-    <row r="45" ht="25.5" spans="1:6">
+    <row r="45" spans="1:6">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" ht="25.5" spans="1:6">
+    <row r="47" spans="1:6">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F47" s="5"/>
     </row>
-    <row r="48" ht="25.5" spans="1:6">
+    <row r="48" spans="1:6">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F50" s="5"/>
     </row>
-    <row r="51" ht="25.5" spans="1:6">
+    <row r="51" spans="1:6">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F51" s="5"/>
     </row>
-    <row r="52" ht="25.5" spans="1:6">
+    <row r="52" spans="1:6">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F57" s="5"/>
     </row>
-    <row r="58" ht="38.25" spans="1:6">
+    <row r="58" ht="25.5" spans="1:6">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
